--- a/results/walkforward/SPY/wf_SPY_1e-07_0.001_8_5.xlsx
+++ b/results/walkforward/SPY/wf_SPY_1e-07_0.001_8_5.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="50" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="100" uniqueCount="42">
   <si>
     <t>Ticker</t>
   </si>
@@ -378,7 +378,7 @@
         <v>-4.5690856356264682</v>
       </c>
       <c r="H2" s="0">
-        <v>-8.0023602085733891</v>
+        <v>-4.918270671099001</v>
       </c>
       <c r="I2" s="0">
         <v>-19.351436257194486</v>
@@ -387,7 +387,7 @@
         <v>-19.351436257194486</v>
       </c>
       <c r="K2" s="0">
-        <v>-19.3721467406769</v>
+        <v>-19.351436257194599</v>
       </c>
       <c r="L2" s="0">
         <v>-0.19029490039202343</v>
@@ -396,7 +396,7 @@
         <v>-0.19029490039202343</v>
       </c>
       <c r="N2" s="0">
-        <v>-0.42222161957838694</v>
+        <v>-0.2124384366722698</v>
       </c>
       <c r="O2" s="0">
         <v>1</v>
@@ -423,7 +423,7 @@
         <v>0</v>
       </c>
       <c r="W2" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X2" s="0">
         <v>100</v>
@@ -435,13 +435,13 @@
         <v>100</v>
       </c>
       <c r="AA2" s="0">
-        <v>98.406374501992033</v>
+        <v>99.760956175298816</v>
       </c>
       <c r="AB2" s="0">
-        <v>1.5</v>
+        <v>0.29999999999999993</v>
       </c>
       <c r="AC2" s="0">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AD2" s="0">
         <v>4</v>
@@ -459,7 +459,7 @@
         <v>0</v>
       </c>
       <c r="AI2" s="0">
-        <v>-3.4332745729469205</v>
+        <v>-0.34918503547253232</v>
       </c>
       <c r="AJ2" s="0">
         <v>0</v>
@@ -468,7 +468,7 @@
         <v>0</v>
       </c>
       <c r="AL2" s="0">
-        <v>-0.020710483482411224</v>
+        <v>-1.1102230246251565e-13</v>
       </c>
       <c r="AM2" s="0">
         <v>0</v>
@@ -477,7 +477,7 @@
         <v>0</v>
       </c>
       <c r="AO2" s="0">
-        <v>-0.23192671918636351</v>
+        <v>-0.022143536280246373</v>
       </c>
     </row>
     <row r="3">
@@ -503,7 +503,7 @@
         <v>31.221575745812657</v>
       </c>
       <c r="H3" s="0">
-        <v>31.089532766683693</v>
+        <v>31.195167149987178</v>
       </c>
       <c r="I3" s="0">
         <v>-6.6194338784514422</v>
@@ -512,7 +512,7 @@
         <v>-6.6194338784514422</v>
       </c>
       <c r="K3" s="0">
-        <v>-6.6194338784514306</v>
+        <v>-6.6194338784513747</v>
       </c>
       <c r="L3" s="0">
         <v>2.235235634639432</v>
@@ -521,7 +521,7 @@
         <v>2.235235634639432</v>
       </c>
       <c r="N3" s="0">
-        <v>2.2270993973017106</v>
+        <v>2.2336199171479634</v>
       </c>
       <c r="O3" s="0">
         <v>1</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="AI3" s="0">
-        <v>-0.13204297912896568</v>
+        <v>-0.026408595825477832</v>
       </c>
       <c r="AJ3" s="0">
         <v>0</v>
@@ -593,7 +593,7 @@
         <v>0</v>
       </c>
       <c r="AL3" s="0">
-        <v>1.1102230246251565e-14</v>
+        <v>6.6613381477509392e-14</v>
       </c>
       <c r="AM3" s="0">
         <v>0</v>
@@ -602,7 +602,7 @@
         <v>0</v>
       </c>
       <c r="AO3" s="0">
-        <v>-0.008136237337721397</v>
+        <v>-0.0016157174914686045</v>
       </c>
     </row>
     <row r="4">
@@ -628,7 +628,7 @@
         <v>38.682879360126222</v>
       </c>
       <c r="H4" s="0">
-        <v>41.858408421578574</v>
+        <v>39.744767499705766</v>
       </c>
       <c r="I4" s="0">
         <v>-33.715385820778579</v>
@@ -637,7 +637,7 @@
         <v>-13.518961923504635</v>
       </c>
       <c r="K4" s="0">
-        <v>-12.430243974198675</v>
+        <v>-12.856780772841558</v>
       </c>
       <c r="L4" s="0">
         <v>0.67018718454210757</v>
@@ -646,7 +646,7 @@
         <v>1.60947251735417</v>
       </c>
       <c r="N4" s="0">
-        <v>1.7512634821607103</v>
+        <v>1.6500465953602153</v>
       </c>
       <c r="O4" s="0">
         <v>1</v>
@@ -685,7 +685,7 @@
         <v>92.490118577075094</v>
       </c>
       <c r="AA4" s="0">
-        <v>91.897233201581031</v>
+        <v>92.351778656126484</v>
       </c>
       <c r="AB4" s="0">
         <v>2</v>
@@ -709,7 +709,7 @@
         <v>20.347069653190132</v>
       </c>
       <c r="AI4" s="0">
-        <v>23.522598714642484</v>
+        <v>21.408957792769677</v>
       </c>
       <c r="AJ4" s="0">
         <v>0</v>
@@ -718,7 +718,7 @@
         <v>20.196423897273942</v>
       </c>
       <c r="AL4" s="0">
-        <v>21.285141846579904</v>
+        <v>20.858605047937019</v>
       </c>
       <c r="AM4" s="0">
         <v>0</v>
@@ -727,7 +727,7 @@
         <v>0.93928533281206239</v>
       </c>
       <c r="AO4" s="0">
-        <v>1.0810762976186026</v>
+        <v>0.97985941081810768</v>
       </c>
     </row>
     <row r="5">
@@ -878,7 +878,7 @@
         <v>-18.172028536815223</v>
       </c>
       <c r="H6" s="0">
-        <v>-24.139391857752056</v>
+        <v>-20.182077986701643</v>
       </c>
       <c r="I6" s="0">
         <v>-24.495450885579995</v>
@@ -887,7 +887,7 @@
         <v>-24.495450885579995</v>
       </c>
       <c r="K6" s="0">
-        <v>-30.001674110873722</v>
+        <v>-26.350169690135061</v>
       </c>
       <c r="L6" s="0">
         <v>-0.70940817269533907</v>
@@ -896,7 +896,7 @@
         <v>-0.70940817269533907</v>
       </c>
       <c r="N6" s="0">
-        <v>-1.0657518350180681</v>
+        <v>-0.82380820608053618</v>
       </c>
       <c r="O6" s="0">
         <v>1</v>
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="W6" s="0">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="X6" s="0">
         <v>100</v>
@@ -935,16 +935,16 @@
         <v>100</v>
       </c>
       <c r="AA6" s="0">
-        <v>96.613545816733065</v>
+        <v>98.98406374501991</v>
       </c>
       <c r="AB6" s="0">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="AC6" s="0">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AD6" s="0">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE6" s="0">
         <v>0.875</v>
@@ -959,7 +959,7 @@
         <v>0</v>
       </c>
       <c r="AI6" s="0">
-        <v>-5.967363320936836</v>
+        <v>-2.0100494498864196</v>
       </c>
       <c r="AJ6" s="0">
         <v>0</v>
@@ -968,7 +968,7 @@
         <v>0</v>
       </c>
       <c r="AL6" s="0">
-        <v>-5.5062232252937271</v>
+        <v>-1.8547188045550667</v>
       </c>
       <c r="AM6" s="0">
         <v>0</v>
@@ -977,7 +977,7 @@
         <v>0</v>
       </c>
       <c r="AO6" s="0">
-        <v>-0.35634366232272907</v>
+        <v>-0.11440003338519711</v>
       </c>
     </row>
     <row r="7">
@@ -1253,7 +1253,7 @@
         <v>16.702577170503385</v>
       </c>
       <c r="H9" s="0">
-        <v>17.774873089791178</v>
+        <v>16.864906598537633</v>
       </c>
       <c r="I9" s="0">
         <v>-18.755277437767138</v>
@@ -1262,7 +1262,7 @@
         <v>-18.755277437767138</v>
       </c>
       <c r="K9" s="0">
-        <v>-19.14146047812514</v>
+        <v>-18.755277437767138</v>
       </c>
       <c r="L9" s="0">
         <v>0.89546472171375724</v>
@@ -1271,7 +1271,7 @@
         <v>0.89546472171375724</v>
       </c>
       <c r="N9" s="0">
-        <v>0.96079510518661948</v>
+        <v>0.9037443134385138</v>
       </c>
       <c r="O9" s="0">
         <v>1</v>
@@ -1298,7 +1298,7 @@
         <v>0</v>
       </c>
       <c r="W9" s="0">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="X9" s="0">
         <v>100</v>
@@ -1310,16 +1310,16 @@
         <v>100</v>
       </c>
       <c r="AA9" s="0">
-        <v>98.900000000000006</v>
+        <v>99.879999999999995</v>
       </c>
       <c r="AB9" s="0">
-        <v>1.5</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="AC9" s="0">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AD9" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE9" s="0">
         <v>0.75</v>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="AI9" s="0">
-        <v>1.0722959192877912</v>
+        <v>0.16232942803424688</v>
       </c>
       <c r="AJ9" s="0">
         <v>0</v>
@@ -1343,7 +1343,7 @@
         <v>0</v>
       </c>
       <c r="AL9" s="0">
-        <v>-0.38618304035800133</v>
+        <v>0</v>
       </c>
       <c r="AM9" s="0">
         <v>0</v>
@@ -1352,7 +1352,7 @@
         <v>0</v>
       </c>
       <c r="AO9" s="0">
-        <v>0.065330383472862241</v>
+        <v>0.0082795917247565631</v>
       </c>
     </row>
     <row r="10">
